--- a/data/trans_camb/P2A_psíq_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_psíq_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 2,36</t>
+          <t>-0,3; 2,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,75</t>
+          <t>-1,04; 0,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,37</t>
+          <t>0,71; 3,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 3,27</t>
+          <t>-1,53; 3,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 0,81</t>
+          <t>-2,83; 0,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,89</t>
+          <t>-1,14; 2,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 2,13</t>
+          <t>-0,37; 1,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,46</t>
+          <t>-1,32; 0,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,69</t>
+          <t>0,36; 2,7</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-71,72; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -793,37 +793,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,77; —</t>
+          <t>-9,15; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-64,13; 469,88</t>
+          <t>-65,3; 457,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 156,55</t>
+          <t>-100,0; 198,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,57; 382,39</t>
+          <t>-43,91; 436,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,12; 444,47</t>
+          <t>-34,03; 373,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-87,16; 127,22</t>
+          <t>-86,47; 136,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,59; 501,11</t>
+          <t>16,68; 640,7</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 4,0</t>
+          <t>-0,23; 4,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,73</t>
+          <t>-1,53; 1,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,37</t>
+          <t>-0,81; 2,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 1,04</t>
+          <t>-1,3; 1,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,56</t>
+          <t>-0,73; 2,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 3,02</t>
+          <t>0,13; 3,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 2,15</t>
+          <t>-0,43; 2,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,67</t>
+          <t>-0,66; 1,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 2,12</t>
+          <t>0,11; 2,26</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-65,84; 1325,63</t>
+          <t>-57,95; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,08; 754,87</t>
+          <t>-61,3; 1023,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-84,61; 1274,67</t>
+          <t>-76,16; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,05; 1103,67</t>
+          <t>-13,98; 1098,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-44,35; 539,18</t>
+          <t>-52,67; 636,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-54,63; 412,51</t>
+          <t>-61,59; 410,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 522,26</t>
+          <t>-4,59; 651,02</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,2</t>
+          <t>0,87; 4,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,25</t>
+          <t>-0,69; 1,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,18</t>
+          <t>-0,72; 2,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 1,91</t>
+          <t>-2,4; 1,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 1,22</t>
+          <t>-2,84; 1,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 3,31</t>
+          <t>-1,54; 3,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,95</t>
+          <t>0,4; 3,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,97</t>
+          <t>-0,7; 0,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,93</t>
+          <t>-0,58; 1,78</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>35,97; 1983,63</t>
+          <t>43,63; 2332,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-84,37; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-53,12; 1247,66</t>
+          <t>-67,1; 1038,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,31; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 898,0</t>
+          <t>16,26; 1086,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-81,63; 412,79</t>
+          <t>-79,68; 315,77</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-54,12; 520,42</t>
+          <t>-44,71; 506,03</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 1,15</t>
+          <t>-0,62; 1,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,37</t>
+          <t>-1,1; 0,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 1,99</t>
+          <t>0,1; 2,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,57</t>
+          <t>-0,31; 2,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,22</t>
+          <t>-1,23; 1,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 58,05</t>
+          <t>0,6; 52,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 1,38</t>
+          <t>-0,23; 1,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,44</t>
+          <t>-0,87; 0,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 36,11</t>
+          <t>0,83; 39,97</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-48,37; 205,45</t>
+          <t>-46,83; 198,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-80,3; 79,63</t>
+          <t>-77,78; 77,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 330,39</t>
+          <t>-6,6; 330,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-23,22; 324,23</t>
+          <t>-23,47; 280,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-55,9; 150,82</t>
+          <t>-58,14; 160,76</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,89; 9507,24</t>
+          <t>38,86; 6988,32</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-18,02; 174,24</t>
+          <t>-17,18; 169,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-56,05; 57,39</t>
+          <t>-57,58; 54,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>59,13; 4438,89</t>
+          <t>65,39; 5434,66</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,93</t>
+          <t>-0,82; 1,91</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 2,54</t>
+          <t>-0,37; 2,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,92</t>
+          <t>0,17; 3,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,93</t>
+          <t>1,17; 4,03</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,91</t>
+          <t>0,91; 3,82</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,08</t>
+          <t>0,78; 3,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,77</t>
+          <t>0,65; 2,69</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,74</t>
+          <t>0,74; 2,89</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,04</t>
+          <t>1,08; 3,04</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-69,38; 896,19</t>
+          <t>-72,3; 721,08</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-41,33; 1035,91</t>
+          <t>-54,05; 907,42</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-12,08; —</t>
+          <t>-8,18; 1347,42</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>52,72; 2111,65</t>
+          <t>68,5; 2032,15</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>42,33; 2252,46</t>
+          <t>44,2; 2083,83</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>52,86; 1682,47</t>
+          <t>49,62; 2208,29</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,97; 943,98</t>
+          <t>40,14; 938,43</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>61,65; 962,16</t>
+          <t>48,57; 1040,48</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>80,98; 1027,17</t>
+          <t>68,46; 1106,63</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 5,34</t>
+          <t>-1,1; 5,29</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 1,68</t>
+          <t>-3,0; 2,05</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 5,1</t>
+          <t>-1,79; 5,16</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,77</t>
+          <t>-0,4; 1,76</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,09</t>
+          <t>-0,89; 1,12</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,83</t>
+          <t>1,05; 3,83</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 1,96</t>
+          <t>-0,12; 1,92</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,94</t>
+          <t>-0,95; 0,81</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,49</t>
+          <t>0,77; 3,3</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-44,47; 506,03</t>
+          <t>-47,11; 523,21</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-82,95; 224,08</t>
+          <t>-82,49; 224,2</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-67,87; 440,0</t>
+          <t>-62,03; 509,33</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-24,72; 184,04</t>
+          <t>-27,96; 200,37</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-55,12; 130,75</t>
+          <t>-56,44; 142,75</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>52,51; 408,12</t>
+          <t>49,17; 432,6</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 184,04</t>
+          <t>-11,21; 167,73</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-51,0; 90,11</t>
+          <t>-49,49; 79,14</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>32,94; 314,58</t>
+          <t>39,87; 315,54</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,61</t>
+          <t>0,39; 1,56</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,48</t>
+          <t>-0,47; 0,47</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,78</t>
+          <t>0,47; 1,72</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,49</t>
+          <t>0,36; 1,56</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 1,09</t>
+          <t>-0,1; 1,05</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,4; 24,4</t>
+          <t>1,33; 23,96</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,37</t>
+          <t>0,49; 1,34</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 0,61</t>
+          <t>-0,13; 0,66</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,22; 14,11</t>
+          <t>1,19; 14,33</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>27,48; 221,04</t>
+          <t>30,54; 228,66</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-40,85; 69,77</t>
+          <t>-41,46; 70,05</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>34,41; 260,17</t>
+          <t>39,82; 251,84</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>17,33; 159,15</t>
+          <t>23,5; 170,35</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 114,66</t>
+          <t>-9,22; 113,51</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>110,02; 2480,67</t>
+          <t>103,99; 2316,96</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>43,52; 158,94</t>
+          <t>38,64; 155,41</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 68,88</t>
+          <t>-12,17; 77,52</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>111,47; 1578,62</t>
+          <t>111,19; 1560,73</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_psíq_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_psíq_R-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>1,97</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 2,19</t>
+          <t>-0,18; 2,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,54</t>
+          <t>-0,9; 0,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,57</t>
+          <t>0,72; 3,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 3,38</t>
+          <t>-1,63; 3,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 0,84</t>
+          <t>-2,97; 0,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 2,82</t>
+          <t>-1,65; 2,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,91</t>
+          <t>-0,33; 2,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,45</t>
+          <t>-1,22; 0,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,7</t>
+          <t>0,32; 2,68</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>431,3%</t>
+          <t>462,97%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>157,33%</t>
+          <t>157,17%</t>
         </is>
       </c>
     </row>
@@ -793,37 +793,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,15; —</t>
+          <t>2,14; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-65,3; 457,56</t>
+          <t>-64,38; 445,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 198,85</t>
+          <t>-100,0; 147,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,91; 436,33</t>
+          <t>-55,44; 340,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,03; 373,64</t>
+          <t>-29,97; 456,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-86,47; 136,89</t>
+          <t>-87,17; 146,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,68; 640,7</t>
+          <t>5,7; 578,05</t>
         </is>
       </c>
     </row>
@@ -850,22 +850,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>0,72</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>-0,17</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>0,77</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,17</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,77</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,57</t>
+          <t>1,69</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>1,18</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 4,24</t>
+          <t>-0,31; 3,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 1,76</t>
+          <t>-1,39; 1,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 2,38</t>
+          <t>-1,09; 2,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,26</t>
+          <t>-1,39; 1,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 2,71</t>
+          <t>-0,55; 2,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 3,07</t>
+          <t>0,27; 3,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 2,31</t>
+          <t>-0,36; 2,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,65</t>
+          <t>-0,64; 1,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,26</t>
+          <t>0,04; 2,28</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>198,65%</t>
+          <t>214,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>134,87%</t>
+          <t>139,04%</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-57,95; —</t>
+          <t>-65,61; 1442,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-61,3; 1023,94</t>
+          <t>-73,72; 750,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-76,16; —</t>
+          <t>-73,21; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 1098,4</t>
+          <t>-8,51; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-52,67; 636,66</t>
+          <t>-42,88; 544,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-61,59; 410,79</t>
+          <t>-58,28; 442,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 651,02</t>
+          <t>-5,34; 612,39</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,7</t>
+          <t>1,28</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>1,14</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,29</t>
+          <t>0,78; 4,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,28</t>
+          <t>-0,68; 1,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 2,1</t>
+          <t>0,06; 2,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,88</t>
+          <t>-2,45; 1,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 1,21</t>
+          <t>-2,8; 1,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 3,01</t>
+          <t>-1,93; 2,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,04</t>
+          <t>0,47; 2,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,98</t>
+          <t>-0,82; 0,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,78</t>
+          <t>0,02; 2,32</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>130,06%</t>
+          <t>237,72%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>101,17%</t>
+          <t>166,62%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>43,63; 2332,91</t>
+          <t>35,57; 1869,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-67,1; 1038,61</t>
+          <t>-21,35; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-85,31; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,26; 1086,11</t>
+          <t>26,72; 1084,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-79,68; 315,77</t>
+          <t>-80,54; 374,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-44,71; 506,03</t>
+          <t>-12,56; 830,08</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,47</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11,02</t>
+          <t>1,05</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,03</t>
+          <t>-0,65; 1,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,31</t>
+          <t>-1,24; 0,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,11</t>
+          <t>0,01; 1,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,52</t>
+          <t>-0,52; 2,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,2</t>
+          <t>-1,22; 1,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 52,04</t>
+          <t>-0,14; 2,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,29</t>
+          <t>-0,22; 1,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,42</t>
+          <t>-0,82; 0,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,83; 39,97</t>
+          <t>0,26; 1,78</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>108,6%</t>
+          <t>100,67%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1512,88%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>977,79%</t>
+          <t>93,0%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-46,83; 198,0</t>
+          <t>-48,33; 212,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-77,78; 77,21</t>
+          <t>-80,78; 58,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 330,94</t>
+          <t>-5,59; 313,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-23,47; 280,44</t>
+          <t>-28,15; 300,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,14; 160,76</t>
+          <t>-61,94; 180,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,86; 6988,32</t>
+          <t>-15,45; 288,99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 169,41</t>
+          <t>-19,05; 177,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-57,58; 54,05</t>
+          <t>-57,86; 59,33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>65,39; 5434,66</t>
+          <t>12,96; 233,5</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,91</t>
+          <t>1,79</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,09</t>
+          <t>2,42</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,02</t>
+          <t>2,17</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,91</t>
+          <t>-0,79; 1,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 2,51</t>
+          <t>-0,39; 2,54</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,17; 3,61</t>
+          <t>0,09; 3,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,03</t>
+          <t>0,93; 3,61</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,82</t>
+          <t>0,95; 3,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,28</t>
+          <t>1,3; 3,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,69</t>
+          <t>0,81; 2,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,89</t>
+          <t>0,71; 2,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,04</t>
+          <t>1,18; 3,07</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>238,88%</t>
+          <t>223,92%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>379,18%</t>
+          <t>439,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>312,82%</t>
+          <t>336,16%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-72,3; 721,08</t>
+          <t>-73,01; 730,94</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-54,05; 907,42</t>
+          <t>-52,37; 830,92</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 1347,42</t>
+          <t>-20,3; 1000,13</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>68,5; 2032,15</t>
+          <t>40,93; 2276,76</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>44,2; 2083,83</t>
+          <t>43,57; 2412,81</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>49,62; 2208,29</t>
+          <t>63,07; 1857,64</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,14; 938,43</t>
+          <t>38,6; 827,81</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>48,57; 1040,48</t>
+          <t>44,68; 911,26</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>68,46; 1106,63</t>
+          <t>81,64; 1013,22</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>2,33</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,26</t>
+          <t>2,38</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,98</t>
+          <t>2,4</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 5,29</t>
+          <t>-1,13; 5,4</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 2,05</t>
+          <t>-3,28; 1,56</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 5,16</t>
+          <t>-0,98; 7,01</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 1,76</t>
+          <t>-0,39; 1,75</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,12</t>
+          <t>-0,85; 1,2</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,83</t>
+          <t>1,17; 3,83</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 1,92</t>
+          <t>-0,13; 1,91</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,81</t>
+          <t>-0,97; 0,85</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,3</t>
+          <t>1,12; 3,93</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>102,11%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>176,74%</t>
+          <t>186,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>134,28%</t>
+          <t>162,93%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-47,11; 523,21</t>
+          <t>-46,26; 504,55</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-82,49; 224,2</t>
+          <t>-84,46; 195,19</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-62,03; 509,33</t>
+          <t>-43,7; 830,28</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-27,96; 200,37</t>
+          <t>-25,51; 230,81</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-56,44; 142,75</t>
+          <t>-52,53; 160,7</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>49,17; 432,6</t>
+          <t>59,49; 452,91</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 167,73</t>
+          <t>-10,56; 188,6</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-49,49; 79,14</t>
+          <t>-52,2; 83,54</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>39,87; 315,54</t>
+          <t>58,28; 344,68</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>1,33</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,13</t>
+          <t>1,67</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4,21</t>
+          <t>1,51</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,56</t>
+          <t>0,37; 1,59</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,47</t>
+          <t>-0,46; 0,56</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,72</t>
+          <t>0,75; 2,03</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,56</t>
+          <t>0,31; 1,52</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 1,05</t>
+          <t>-0,14; 1,03</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,33; 23,96</t>
+          <t>1,06; 2,28</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,34</t>
+          <t>0,54; 1,4</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 0,66</t>
+          <t>-0,12; 0,64</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,19; 14,33</t>
+          <t>1,09; 1,95</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>123,04%</t>
+          <t>146,18%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>610,41%</t>
+          <t>142,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>404,84%</t>
+          <t>144,63%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>30,54; 228,66</t>
+          <t>29,67; 233,42</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-41,46; 70,05</t>
+          <t>-40,25; 79,89</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>39,82; 251,84</t>
+          <t>61,39; 290,88</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>23,5; 170,35</t>
+          <t>20,6; 162,2</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 113,51</t>
+          <t>-10,43; 107,73</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>103,99; 2316,96</t>
+          <t>73,9; 252,91</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>38,64; 155,41</t>
+          <t>42,7; 159,05</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-12,17; 77,52</t>
+          <t>-11,21; 75,2</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>111,19; 1560,73</t>
+          <t>86,5; 223,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_psíq_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_psíq_R-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad psíquica</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
